--- a/data/trans_bre/IP13-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Estudios-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-2,49</t>
+          <t>-2,32</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-21,71%</t>
+          <t>-19,08%</t>
         </is>
       </c>
     </row>
@@ -660,32 +660,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 3,95</t>
+          <t>-7,57; 3,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,2</t>
+          <t>-7,83; 4,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,66; 6,38</t>
+          <t>-5,32; 5,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 6,13</t>
+          <t>-11,94; 7,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-77,44; 131,74</t>
+          <t>-72,74; 159,92</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-68,28; 115,39</t>
+          <t>-69,43; 103,62</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -695,7 +695,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-72,77; 108,57</t>
+          <t>-71,38; 139,52</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,83</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-14,45%</t>
+          <t>-12,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 3,01</t>
+          <t>-1,69; 2,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,07</t>
+          <t>-4,04; 0,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 2,33</t>
+          <t>-2,49; 2,31</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,52; 1,6</t>
+          <t>-3,01; 1,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-30,45; 89,62</t>
+          <t>-31,36; 82,87</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-50,91; 18,81</t>
+          <t>-49,53; 17,51</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,23; 63,02</t>
+          <t>-39,42; 63,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-50,31; 37,55</t>
+          <t>-44,1; 36,46</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,27</t>
+          <t>0,12</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,34; 0,38</t>
+          <t>-6,31; 0,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 5,74</t>
+          <t>-1,71; 5,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 6,71</t>
+          <t>-0,81; 6,29</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 6,07</t>
+          <t>-5,02; 5,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-80,74; 20,44</t>
+          <t>-80,87; 38,28</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-41,02; 356,59</t>
+          <t>-39,4; 433,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-22,07; 354,42</t>
+          <t>-20,72; 325,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-51,18; 157,23</t>
+          <t>-56,47; 135,28</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,72</t>
+          <t>-0,66</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-11,34%</t>
+          <t>-10,18%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 1,28</t>
+          <t>-2,42; 1,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 1,46</t>
+          <t>-2,56; 1,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 2,77</t>
+          <t>-0,82; 2,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,05; 1,43</t>
+          <t>-2,95; 1,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-39,1; 33,57</t>
+          <t>-41,83; 29,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-36,47; 27,53</t>
+          <t>-37,43; 27,8</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-17,81; 78,47</t>
+          <t>-17,21; 74,36</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,08; 26,38</t>
+          <t>-39,04; 27,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP13-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP13-Estudios-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-1,77</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-2,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-25,36%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-17,69%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>7,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-19,08%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-1.767564661178427</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.422791285268121</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.2473790760301672</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-2.320717990311821</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2536295195066899</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.1769275647970463</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.0758184713324823</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.1907629441254791</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-7,57; 3,84</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 4,37</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-5,32; 5,17</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,94; 7,82</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-72,74; 159,92</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-69,43; 103,62</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-71,38; 139,52</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-7.574184266269171</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-7.833345103818141</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-5.317562829526393</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-11.93663137243244</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.7273966205679785</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.6943369433017212</v>
+      </c>
+      <c r="I5" s="6" t="inlineStr"/>
+      <c r="J5" s="6" t="n">
+        <v>-0.7138122016416798</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.840710358623874</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>4.36836141199951</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>5.1658124664227</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>7.821435866507167</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>1.599156686269438</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>1.036192581655505</v>
+      </c>
+      <c r="I6" s="6" t="inlineStr"/>
+      <c r="J6" s="6" t="n">
+        <v>1.395240826355927</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Secundarios</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,51</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,53</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,14</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,23%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-22,32%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,96%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-12,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-1,69; 2,85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-4,04; 0,98</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,49; 2,31</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-3,01; 1,63</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-31,36; 82,87</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-49,53; 17,51</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-39,42; 63,56</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-44,1; 36,46</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.5066449835019373</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.530220508794605</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>0.1446415445595754</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-0.6937363596662873</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.1123070073923374</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.223241585337297</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.0295553266716141</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.1203915847913242</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Universitarios</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-2,65</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,91</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2,89</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,12</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-49,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>59,98%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,45%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-1.690234604236986</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-4.042823177237342</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.486698644738693</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-3.005906633835177</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3136065375151039</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.495335717127706</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3941898301155121</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.4409674363835062</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,31; 0,52</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-1,71; 5,97</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-0,81; 6,29</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-5,02; 5,06</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-80,87; 38,28</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-39,4; 433,84</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-20,72; 325,51</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-56,47; 135,28</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.850591776376092</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>0.9798268521519875</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>2.312463349449096</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>1.632654230066053</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.8286960636093976</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.175144870035736</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6356391537851894</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3645573599742615</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Universitarios</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,97 +815,197 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,54</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0,85</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,66</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-10,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-11,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-10,18%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-2.651982050075536</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.911183365446053</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>2.887110656666318</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>0.1225654262319353</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.4899786978961767</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.5998304395294517</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.8044856162922416</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.01817586000838343</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-2,42; 1,15</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-2,56; 1,5</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-0,82; 2,67</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-2,95; 1,53</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,83; 29,57</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-37,43; 27,8</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-17,21; 74,36</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-39,04; 27,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.313555194721491</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-1.706712901801055</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-0.8143935883233979</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-5.02153723971602</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.8087208348879684</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.3940468458696947</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.20721690357593</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.564679094672086</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>0.5195026070935342</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>5.965205948428159</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.292545383837947</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>5.056214549845038</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.382756784464465</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>4.338353132805808</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>3.255053212674967</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.352763439036592</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-0.53888682491256</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-0.71013705948373</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>0.8470050451875599</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.6632328921381867</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1076849573161558</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.1154996679552896</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>0.1918416343656075</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1017816028352304</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-2.418831316364427</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-2.563215144912954</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-0.8196046135442451</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-2.95162634520258</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4183373936948908</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.3743366933564745</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1720618312356546</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3904437188558234</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>1.154448091528447</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.502901232250638</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.672001923249898</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>1.5304856193095</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.2957441267249541</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.2780350845027756</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.7435611600403741</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2750664298154697</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1008,13 +1013,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
